--- a/results/supplementary/tables_submission/TableS9_permanova_balanced_iterado.xlsx
+++ b/results/supplementary/tables_submission/TableS9_permanova_balanced_iterado.xlsx
@@ -50,10 +50,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,43 +79,31 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Cambria"/>
+      <sz val="12"/>
+      <name val="Ubuntu"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Cambria"/>
+      <sz val="12"/>
+      <name val="Ubuntu"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Ubuntu"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2E4057"/>
-        <bgColor rgb="FF333399"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4E6F1"/>
-        <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -158,25 +147,33 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -188,66 +185,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFD4E6F1"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF2E4057"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -434,2050 +371,2050 @@
   <dimension ref="A1:F102"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="4" t="n">
         <v>0.1062</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>424</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.001</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3" t="n">
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="6" t="n">
         <v>0.207884262504423</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="6" t="n">
         <v>92.5107267335641</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F3" s="3" t="n">
+      <c r="E3" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F3" s="6" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="4" t="n">
+      <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="6" t="n">
         <v>0.191202991350445</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="6" t="n">
         <v>83.3324724624883</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F4" s="4" t="n">
+      <c r="E4" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>0.18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3" t="n">
+      <c r="A5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="6" t="n">
         <v>0.205644235776943</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="6" t="n">
         <v>91.2558281518523</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F5" s="3" t="n">
+      <c r="E5" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>0.205</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="4" t="n">
+      <c r="A6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="6" t="n">
         <v>0.20801076356369</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="6" t="n">
         <v>92.5818063969321</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F6" s="4" t="n">
+      <c r="E6" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F6" s="6" t="n">
         <v>0.145</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3" t="n">
+      <c r="A7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="6" t="n">
         <v>0.200264480894505</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="6" t="n">
         <v>88.2707192926375</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F7" s="3" t="n">
+      <c r="E7" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>0.43</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="n">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="6" t="n">
         <v>0.204170237609394</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="6" t="n">
         <v>90.4339246387561</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F8" s="4" t="n">
+      <c r="E8" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F8" s="6" t="n">
         <v>0.125</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="A9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="6" t="n">
         <v>0.206671152018176</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="6" t="n">
         <v>91.830243248732</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F9" s="3" t="n">
+      <c r="E9" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>0.335</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="4" t="n">
+      <c r="A10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="6" t="n">
         <v>0.203789516098665</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="6" t="n">
         <v>90.22212829049</v>
       </c>
-      <c r="E10" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F10" s="4" t="n">
+      <c r="E10" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F10" s="6" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3" t="n">
+      <c r="A11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="6" t="n">
         <v>0.203520918128266</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="6" t="n">
         <v>90.072828368099</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F11" s="3" t="n">
+      <c r="E11" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F11" s="6" t="n">
         <v>0.085</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="4" t="n">
+      <c r="A12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="6" t="n">
         <v>0.186610260650651</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="6" t="n">
         <v>80.8715843059118</v>
       </c>
-      <c r="E12" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F12" s="4" t="n">
+      <c r="E12" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F12" s="6" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="3" t="n">
+      <c r="A13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="6" t="n">
         <v>0.23028092096956</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="6" t="n">
         <v>105.459286190514</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F13" s="3" t="n">
+      <c r="E13" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F13" s="6" t="n">
         <v>0.315</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="4" t="n">
+      <c r="A14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="6" t="n">
         <v>0.232289760642334</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="6" t="n">
         <v>106.657611724617</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F14" s="4" t="n">
+      <c r="E14" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F14" s="6" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="3" t="n">
+      <c r="A15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="6" t="n">
         <v>0.213471800613234</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="6" t="n">
         <v>95.6721065752435</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F15" s="3" t="n">
+      <c r="E15" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F15" s="6" t="n">
         <v>0.015</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="4" t="n">
+      <c r="A16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="6" t="n">
         <v>0.229680519138093</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="6" t="n">
         <v>105.102343907478</v>
       </c>
-      <c r="E16" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F16" s="4" t="n">
+      <c r="E16" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F16" s="6" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="3" t="n">
+      <c r="A17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="6" t="n">
         <v>0.212377493887112</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="6" t="n">
         <v>95.0494253454929</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F17" s="3" t="n">
+      <c r="E17" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F17" s="6" t="n">
         <v>0.295</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="4" t="n">
+      <c r="A18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="6" t="n">
         <v>0.199769724505783</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="6" t="n">
         <v>87.9982050726567</v>
       </c>
-      <c r="E18" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F18" s="4" t="n">
+      <c r="E18" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F18" s="6" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="3" t="n">
+      <c r="A19" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="6" t="n">
         <v>0.208166028854457</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="6" t="n">
         <v>92.66907943472</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F19" s="3" t="n">
+      <c r="E19" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F19" s="6" t="n">
         <v>0.51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="4" t="n">
+      <c r="A20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="6" t="n">
         <v>0.206491210323984</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="6" t="n">
         <v>91.7294837640341</v>
       </c>
-      <c r="E20" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F20" s="4" t="n">
+      <c r="E20" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F20" s="6" t="n">
         <v>0.085</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="3" t="n">
+      <c r="A21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="6" t="n">
         <v>0.208023550611838</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="6" t="n">
         <v>92.5889925733552</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F21" s="3" t="n">
+      <c r="E21" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F21" s="6" t="n">
         <v>0.09</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="4" t="n">
+      <c r="A22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="6" t="n">
         <v>0.205718654297664</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="6" t="n">
         <v>91.2974049211807</v>
       </c>
-      <c r="E22" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F22" s="4" t="n">
+      <c r="E22" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F22" s="6" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="3" t="n">
+      <c r="A23" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="6" t="n">
         <v>0.237481303068022</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="6" t="n">
         <v>109.783746507852</v>
       </c>
-      <c r="E23" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F23" s="3" t="n">
+      <c r="E23" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F23" s="6" t="n">
         <v>0.205</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="4" t="n">
+      <c r="A24" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="6" t="n">
         <v>0.243930963782529</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="6" t="n">
         <v>113.727266445824</v>
       </c>
-      <c r="E24" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F24" s="4" t="n">
+      <c r="E24" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F24" s="6" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="3" t="n">
+      <c r="A25" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="6" t="n">
         <v>0.199882710276821</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="6" t="n">
         <v>88.0604084895558</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F25" s="3" t="n">
+      <c r="E25" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F25" s="6" t="n">
         <v>0.125</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="4" t="n">
+      <c r="A26" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="6" t="n">
         <v>0.212933741231803</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="6" t="n">
         <v>95.3657242297264</v>
       </c>
-      <c r="E26" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F26" s="4" t="n">
+      <c r="E26" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F26" s="6" t="n">
         <v>0.09</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="3" t="n">
+      <c r="A27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C27" s="6" t="n">
         <v>0.221143284633064</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="6" t="n">
         <v>100.086455307033</v>
       </c>
-      <c r="E27" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F27" s="3" t="n">
+      <c r="E27" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F27" s="6" t="n">
         <v>0.015</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="4" t="n">
+      <c r="A28" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="6" t="n">
         <v>0.22973452745579</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="6" t="n">
         <v>105.134429381447</v>
       </c>
-      <c r="E28" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F28" s="4" t="n">
+      <c r="E28" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F28" s="6" t="n">
         <v>0.35</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="3" t="n">
+      <c r="A29" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="6" t="n">
         <v>0.196106007770974</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="6" t="n">
         <v>85.9906510155563</v>
       </c>
-      <c r="E29" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F29" s="3" t="n">
+      <c r="E29" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F29" s="6" t="n">
         <v>0.075</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="4" t="n">
+      <c r="A30" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="6" t="n">
         <v>0.207711941839648</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="6" t="n">
         <v>92.4139380170451</v>
       </c>
-      <c r="E30" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F30" s="4" t="n">
+      <c r="E30" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F30" s="6" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="3" t="n">
+      <c r="A31" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="6" t="n">
         <v>0.187634962852809</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="6" t="n">
         <v>81.4182311906061</v>
       </c>
-      <c r="E31" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F31" s="3" t="n">
+      <c r="E31" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F31" s="6" t="n">
         <v>0.055</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="4" t="n">
+      <c r="A32" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="6" t="n">
         <v>0.234494811424588</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="6" t="n">
         <v>107.98022307464</v>
       </c>
-      <c r="E32" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F32" s="4" t="n">
+      <c r="E32" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F32" s="6" t="n">
         <v>0.14</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="3" t="n">
+      <c r="A33" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="6" t="n">
         <v>0.215370446807896</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="6" t="n">
         <v>96.7565932113141</v>
       </c>
-      <c r="E33" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F33" s="3" t="n">
+      <c r="E33" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F33" s="6" t="n">
         <v>0.015</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="4" t="n">
+      <c r="A34" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="6" t="n">
         <v>0.219136184015857</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="6" t="n">
         <v>98.9231454760587</v>
       </c>
-      <c r="E34" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F34" s="4" t="n">
+      <c r="E34" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F34" s="6" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" s="3" t="n">
+      <c r="A35" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="6" t="n">
         <v>0.226193679706654</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="6" t="n">
         <v>103.040347442974</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F35" s="3" t="n">
+      <c r="E35" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F35" s="6" t="n">
         <v>0.72</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="4" t="n">
+      <c r="A36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="6" t="n">
         <v>0.192894025697852</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="6" t="n">
         <v>84.245621050301</v>
       </c>
-      <c r="E36" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F36" s="4" t="n">
+      <c r="E36" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F36" s="6" t="n">
         <v>0.155</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" s="3" t="n">
+      <c r="A37" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="6" t="n">
         <v>0.211951002595706</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="6" t="n">
         <v>94.8072120655923</v>
       </c>
-      <c r="E37" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F37" s="3" t="n">
+      <c r="E37" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F37" s="6" t="n">
         <v>0.055</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="4" t="n">
+      <c r="A38" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C38" s="6" t="n">
         <v>0.205318229899524</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="6" t="n">
         <v>91.0737842022368</v>
       </c>
-      <c r="E38" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F38" s="4" t="n">
+      <c r="E38" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F38" s="6" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" s="3" t="n">
+      <c r="A39" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C39" s="6" t="n">
         <v>0.195255689425037</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="6" t="n">
         <v>85.5273278951802</v>
       </c>
-      <c r="E39" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F39" s="3" t="n">
+      <c r="E39" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F39" s="6" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="4" t="n">
+      <c r="A40" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="C40" s="4" t="n">
+      <c r="C40" s="6" t="n">
         <v>0.208023676038386</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="6" t="n">
         <v>92.5890630628059</v>
       </c>
-      <c r="E40" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F40" s="4" t="n">
+      <c r="E40" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F40" s="6" t="n">
         <v>0.13</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="3" t="n">
+      <c r="A41" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C41" s="6" t="n">
         <v>0.203178142764654</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="6" t="n">
         <v>89.8824432013378</v>
       </c>
-      <c r="E41" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F41" s="3" t="n">
+      <c r="E41" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F41" s="6" t="n">
         <v>0.19</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" s="4" t="n">
+      <c r="A42" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="6" t="n">
         <v>0.224727468179679</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="6" t="n">
         <v>102.178820069039</v>
       </c>
-      <c r="E42" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F42" s="4" t="n">
+      <c r="E42" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F42" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" s="3" t="n">
+      <c r="A43" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="C43" s="6" t="n">
         <v>0.204453206543966</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="6" t="n">
         <v>90.5914723050556</v>
       </c>
-      <c r="E43" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F43" s="3" t="n">
+      <c r="E43" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F43" s="6" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" s="4" t="n">
+      <c r="A44" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="C44" s="4" t="n">
+      <c r="C44" s="6" t="n">
         <v>0.209332234077771</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="6" t="n">
         <v>93.3256870872261</v>
       </c>
-      <c r="E44" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F44" s="4" t="n">
+      <c r="E44" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F44" s="6" t="n">
         <v>0.02</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" s="3" t="n">
+      <c r="A45" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="C45" s="6" t="n">
         <v>0.198058614585662</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="6" t="n">
         <v>87.0583098855464</v>
       </c>
-      <c r="E45" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F45" s="3" t="n">
+      <c r="E45" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F45" s="6" t="n">
         <v>0.48</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="4" t="n">
+      <c r="A46" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="6" t="n">
         <v>0.233246272762738</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="6" t="n">
         <v>107.230402967997</v>
       </c>
-      <c r="E46" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F46" s="4" t="n">
+      <c r="E46" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F46" s="6" t="n">
         <v>0.195</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" s="3" t="n">
+      <c r="A47" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C47" s="6" t="n">
         <v>0.202392469788706</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="6" t="n">
         <v>89.4466801004492</v>
       </c>
-      <c r="E47" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F47" s="3" t="n">
+      <c r="E47" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F47" s="6" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="4" t="n">
+      <c r="A48" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="C48" s="4" t="n">
+      <c r="C48" s="6" t="n">
         <v>0.219523586581144</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="6" t="n">
         <v>99.1472169298278</v>
       </c>
-      <c r="E48" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F48" s="4" t="n">
+      <c r="E48" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F48" s="6" t="n">
         <v>0.015</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B49" s="3" t="n">
+      <c r="A49" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="C49" s="6" t="n">
         <v>0.197330574021535</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="D49" s="6" t="n">
         <v>86.6596198775079</v>
       </c>
-      <c r="E49" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F49" s="3" t="n">
+      <c r="E49" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F49" s="6" t="n">
         <v>0.315</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50" s="4" t="n">
+      <c r="A50" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="C50" s="4" t="n">
+      <c r="C50" s="6" t="n">
         <v>0.190521134985341</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="6" t="n">
         <v>82.965353371044</v>
       </c>
-      <c r="E50" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F50" s="4" t="n">
+      <c r="E50" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F50" s="6" t="n">
         <v>0.58</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B51" s="3" t="n">
+      <c r="A51" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="C51" s="6" t="n">
         <v>0.218210336464086</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="D51" s="6" t="n">
         <v>98.3885400271177</v>
       </c>
-      <c r="E51" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F51" s="3" t="n">
+      <c r="E51" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F51" s="6" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="4" t="n">
+      <c r="A52" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="C52" s="4" t="n">
+      <c r="C52" s="6" t="n">
         <v>0.215065160749447</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="6" t="n">
         <v>96.581863071033</v>
       </c>
-      <c r="E52" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F52" s="4" t="n">
+      <c r="E52" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F52" s="6" t="n">
         <v>0.115</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" s="3" t="n">
+      <c r="A53" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="C53" s="6" t="n">
         <v>0.205801510884474</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" s="6" t="n">
         <v>91.3437051077348</v>
       </c>
-      <c r="E53" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F53" s="3" t="n">
+      <c r="E53" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F53" s="6" t="n">
         <v>0.085</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54" s="4" t="n">
+      <c r="A54" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="C54" s="4" t="n">
+      <c r="C54" s="6" t="n">
         <v>0.188002838062502</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="6" t="n">
         <v>81.6148177893913</v>
       </c>
-      <c r="E54" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F54" s="4" t="n">
+      <c r="E54" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F54" s="6" t="n">
         <v>0.555</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B55" s="3" t="n">
+      <c r="A55" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="C55" s="6" t="n">
         <v>0.220683541426456</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="D55" s="6" t="n">
         <v>99.8194603707122</v>
       </c>
-      <c r="E55" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F55" s="3" t="n">
+      <c r="E55" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F55" s="6" t="n">
         <v>0.41</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B56" s="4" t="n">
+      <c r="A56" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="C56" s="6" t="n">
         <v>0.205219137114873</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="6" t="n">
         <v>91.018479698156</v>
       </c>
-      <c r="E56" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F56" s="4" t="n">
+      <c r="E56" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F56" s="6" t="n">
         <v>0.485</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B57" s="3" t="n">
+      <c r="A57" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="C57" s="6" t="n">
         <v>0.212992400691758</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="D57" s="6" t="n">
         <v>95.3991058152907</v>
       </c>
-      <c r="E57" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F57" s="3" t="n">
+      <c r="E57" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F57" s="6" t="n">
         <v>0.445</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B58" s="4" t="n">
+      <c r="A58" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="C58" s="4" t="n">
+      <c r="C58" s="6" t="n">
         <v>0.204980342560185</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="6" t="n">
         <v>90.8852631205979</v>
       </c>
-      <c r="E58" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F58" s="4" t="n">
+      <c r="E58" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F58" s="6" t="n">
         <v>0.085</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B59" s="3" t="n">
+      <c r="A59" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="C59" s="6" t="n">
         <v>0.213331790775885</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D59" s="6" t="n">
         <v>95.592341684518</v>
       </c>
-      <c r="E59" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F59" s="3" t="n">
+      <c r="E59" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F59" s="6" t="n">
         <v>0.185</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B60" s="4" t="n">
+      <c r="A60" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="C60" s="4" t="n">
+      <c r="C60" s="6" t="n">
         <v>0.205810964853842</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="6" t="n">
         <v>91.3489885913974</v>
       </c>
-      <c r="E60" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F60" s="4" t="n">
+      <c r="E60" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F60" s="6" t="n">
         <v>0.135</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B61" s="3" t="n">
+      <c r="A61" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="C61" s="6" t="n">
         <v>0.21039605539219</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="D61" s="6" t="n">
         <v>93.9263412147515</v>
       </c>
-      <c r="E61" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F61" s="3" t="n">
+      <c r="E61" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F61" s="6" t="n">
         <v>0.39</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B62" s="4" t="n">
+      <c r="A62" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="C62" s="4" t="n">
+      <c r="C62" s="6" t="n">
         <v>0.205207031147718</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="6" t="n">
         <v>91.0117242028782</v>
       </c>
-      <c r="E62" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F62" s="4" t="n">
+      <c r="E62" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F62" s="6" t="n">
         <v>0.33</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B63" s="3" t="n">
+      <c r="A63" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="C63" s="6" t="n">
         <v>0.235873822428455</v>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="D63" s="6" t="n">
         <v>108.811247208247</v>
       </c>
-      <c r="E63" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F63" s="3" t="n">
+      <c r="E63" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F63" s="6" t="n">
         <v>0.355</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B64" s="4" t="n">
+      <c r="A64" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="C64" s="4" t="n">
+      <c r="C64" s="6" t="n">
         <v>0.227526366632875</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="6" t="n">
         <v>103.826254740233</v>
       </c>
-      <c r="E64" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F64" s="4" t="n">
+      <c r="E64" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F64" s="6" t="n">
         <v>0.07</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B65" s="3" t="n">
+      <c r="A65" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="C65" s="3" t="n">
+      <c r="C65" s="6" t="n">
         <v>0.200088445333742</v>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="D65" s="6" t="n">
         <v>88.1737194177314</v>
       </c>
-      <c r="E65" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F65" s="3" t="n">
+      <c r="E65" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F65" s="6" t="n">
         <v>0.205</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B66" s="4" t="n">
+      <c r="A66" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="C66" s="4" t="n">
+      <c r="C66" s="6" t="n">
         <v>0.193756550990139</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="6" t="n">
         <v>84.7128547933027</v>
       </c>
-      <c r="E66" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F66" s="4" t="n">
+      <c r="E66" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F66" s="6" t="n">
         <v>0.235</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B67" s="3" t="n">
+      <c r="A67" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="C67" s="3" t="n">
+      <c r="C67" s="6" t="n">
         <v>0.192529699499549</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D67" s="6" t="n">
         <v>84.048563806655</v>
       </c>
-      <c r="E67" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F67" s="3" t="n">
+      <c r="E67" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F67" s="6" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B68" s="4" t="n">
+      <c r="A68" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="C68" s="4" t="n">
+      <c r="C68" s="6" t="n">
         <v>0.196128674868863</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="6" t="n">
         <v>86.0030153208863</v>
       </c>
-      <c r="E68" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F68" s="4" t="n">
+      <c r="E68" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F68" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B69" s="3" t="n">
+      <c r="A69" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="C69" s="6" t="n">
         <v>0.210558233769415</v>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="D69" s="6" t="n">
         <v>94.0180524753739</v>
       </c>
-      <c r="E69" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F69" s="3" t="n">
+      <c r="E69" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F69" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B70" s="4" t="n">
+      <c r="A70" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="C70" s="4" t="n">
+      <c r="C70" s="6" t="n">
         <v>0.2108254874732</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="6" t="n">
         <v>94.1692656752892</v>
       </c>
-      <c r="E70" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F70" s="4" t="n">
+      <c r="E70" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F70" s="6" t="n">
         <v>0.31</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B71" s="3" t="n">
+      <c r="A71" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="C71" s="3" t="n">
+      <c r="C71" s="6" t="n">
         <v>0.227477303082566</v>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="D71" s="6" t="n">
         <v>103.797273085395</v>
       </c>
-      <c r="E71" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F71" s="3" t="n">
+      <c r="E71" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F71" s="6" t="n">
         <v>0.31</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B72" s="4" t="n">
+      <c r="A72" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="C72" s="4" t="n">
+      <c r="C72" s="6" t="n">
         <v>0.235580020967179</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="D72" s="6" t="n">
         <v>108.633944256662</v>
       </c>
-      <c r="E72" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F72" s="4" t="n">
+      <c r="E72" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F72" s="6" t="n">
         <v>0.62</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B73" s="3" t="n">
+      <c r="A73" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="C73" s="3" t="n">
+      <c r="C73" s="6" t="n">
         <v>0.195206978865846</v>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="D73" s="6" t="n">
         <v>85.5008160399296</v>
       </c>
-      <c r="E73" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F73" s="3" t="n">
+      <c r="E73" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F73" s="6" t="n">
         <v>0.135</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B74" s="4" t="n">
+      <c r="A74" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="C74" s="4" t="n">
+      <c r="C74" s="6" t="n">
         <v>0.189785721661731</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="6" t="n">
         <v>82.5700912392823</v>
       </c>
-      <c r="E74" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F74" s="4" t="n">
+      <c r="E74" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F74" s="6" t="n">
         <v>0.16</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B75" s="3" t="n">
+      <c r="A75" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="C75" s="3" t="n">
+      <c r="C75" s="6" t="n">
         <v>0.213070364145049</v>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="D75" s="6" t="n">
         <v>95.4434805083054</v>
       </c>
-      <c r="E75" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F75" s="3" t="n">
+      <c r="E75" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F75" s="6" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B76" s="4" t="n">
+      <c r="A76" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="C76" s="4" t="n">
+      <c r="C76" s="6" t="n">
         <v>0.250712269460555</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="6" t="n">
         <v>117.946779832121</v>
       </c>
-      <c r="E76" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F76" s="4" t="n">
+      <c r="E76" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F76" s="6" t="n">
         <v>0.105</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B77" s="3" t="n">
+      <c r="A77" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="C77" s="6" t="n">
         <v>0.193669644744645</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D77" s="6" t="n">
         <v>84.6657320136079</v>
       </c>
-      <c r="E77" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F77" s="3" t="n">
+      <c r="E77" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F77" s="6" t="n">
         <v>0.96</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" s="4" t="n">
+      <c r="A78" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="C78" s="4" t="n">
+      <c r="C78" s="6" t="n">
         <v>0.233249282972192</v>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="D78" s="6" t="n">
         <v>107.232207837265</v>
       </c>
-      <c r="E78" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F78" s="4" t="n">
+      <c r="E78" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F78" s="6" t="n">
         <v>0.185</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B79" s="3" t="n">
+      <c r="A79" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="C79" s="3" t="n">
+      <c r="C79" s="6" t="n">
         <v>0.23614721137843</v>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="D79" s="6" t="n">
         <v>108.976354149486</v>
       </c>
-      <c r="E79" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F79" s="3" t="n">
+      <c r="E79" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F79" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B80" s="4" t="n">
+      <c r="A80" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="C80" s="4" t="n">
+      <c r="C80" s="6" t="n">
         <v>0.195984534822672</v>
       </c>
-      <c r="D80" s="4" t="n">
+      <c r="D80" s="6" t="n">
         <v>85.9244025980955</v>
       </c>
-      <c r="E80" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F80" s="4" t="n">
+      <c r="E80" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F80" s="6" t="n">
         <v>0.74</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B81" s="3" t="n">
+      <c r="A81" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B81" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="C81" s="3" t="n">
+      <c r="C81" s="6" t="n">
         <v>0.216441876209121</v>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="D81" s="6" t="n">
         <v>97.3709021030807</v>
       </c>
-      <c r="E81" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F81" s="3" t="n">
+      <c r="E81" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F81" s="6" t="n">
         <v>0.395</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B82" s="4" t="n">
+      <c r="A82" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="C82" s="4" t="n">
+      <c r="C82" s="6" t="n">
         <v>0.221599874961265</v>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="D82" s="6" t="n">
         <v>100.351931366865</v>
       </c>
-      <c r="E82" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F82" s="4" t="n">
+      <c r="E82" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F82" s="6" t="n">
         <v>0.225</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B83" s="3" t="n">
+      <c r="A83" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="C83" s="3" t="n">
+      <c r="C83" s="6" t="n">
         <v>0.217030090344648</v>
       </c>
-      <c r="D83" s="3" t="n">
+      <c r="D83" s="6" t="n">
         <v>97.7088722096148</v>
       </c>
-      <c r="E83" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F83" s="3" t="n">
+      <c r="E83" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F83" s="6" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B84" s="4" t="n">
+      <c r="A84" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="C84" s="4" t="n">
+      <c r="C84" s="6" t="n">
         <v>0.190971947099287</v>
       </c>
-      <c r="D84" s="4" t="n">
+      <c r="D84" s="6" t="n">
         <v>83.2080063369077</v>
       </c>
-      <c r="E84" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F84" s="4" t="n">
+      <c r="E84" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F84" s="6" t="n">
         <v>0.055</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B85" s="3" t="n">
+      <c r="A85" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="C85" s="3" t="n">
+      <c r="C85" s="6" t="n">
         <v>0.195943961824161</v>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D85" s="6" t="n">
         <v>85.9022795223532</v>
       </c>
-      <c r="E85" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F85" s="3" t="n">
+      <c r="E85" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F85" s="6" t="n">
         <v>0.605</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B86" s="4" t="n">
+      <c r="A86" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="C86" s="4" t="n">
+      <c r="C86" s="6" t="n">
         <v>0.208153255823774</v>
       </c>
-      <c r="D86" s="4" t="n">
+      <c r="D86" s="6" t="n">
         <v>92.661898552368</v>
       </c>
-      <c r="E86" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F86" s="4" t="n">
+      <c r="E86" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F86" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B87" s="3" t="n">
+      <c r="A87" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="C87" s="3" t="n">
+      <c r="C87" s="6" t="n">
         <v>0.246761695664606</v>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="D87" s="6" t="n">
         <v>115.479387095856</v>
       </c>
-      <c r="E87" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F87" s="3" t="n">
+      <c r="E87" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F87" s="6" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B88" s="4" t="n">
+      <c r="A88" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="C88" s="4" t="n">
+      <c r="C88" s="6" t="n">
         <v>0.190648954412505</v>
       </c>
-      <c r="D88" s="4" t="n">
+      <c r="D88" s="6" t="n">
         <v>83.0341256699385</v>
       </c>
-      <c r="E88" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F88" s="4" t="n">
+      <c r="E88" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F88" s="6" t="n">
         <v>0.61</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B89" s="3" t="n">
+      <c r="A89" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="C89" s="3" t="n">
+      <c r="C89" s="6" t="n">
         <v>0.194851077990293</v>
       </c>
-      <c r="D89" s="3" t="n">
+      <c r="D89" s="6" t="n">
         <v>85.3072060509447</v>
       </c>
-      <c r="E89" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F89" s="3" t="n">
+      <c r="E89" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F89" s="6" t="n">
         <v>0.59</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B90" s="4" t="n">
+      <c r="A90" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="C90" s="4" t="n">
+      <c r="C90" s="6" t="n">
         <v>0.238195970428517</v>
       </c>
-      <c r="D90" s="4" t="n">
+      <c r="D90" s="6" t="n">
         <v>110.217426420391</v>
       </c>
-      <c r="E90" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F90" s="4" t="n">
+      <c r="E90" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F90" s="6" t="n">
         <v>0.24</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B91" s="3" t="n">
+      <c r="A91" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="C91" s="3" t="n">
+      <c r="C91" s="6" t="n">
         <v>0.236007377580432</v>
       </c>
-      <c r="D91" s="3" t="n">
+      <c r="D91" s="6" t="n">
         <v>108.891889994475</v>
       </c>
-      <c r="E91" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F91" s="3" t="n">
+      <c r="E91" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F91" s="6" t="n">
         <v>0.095</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B92" s="4" t="n">
+      <c r="A92" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="C92" s="4" t="n">
+      <c r="C92" s="6" t="n">
         <v>0.192167597428379</v>
       </c>
-      <c r="D92" s="4" t="n">
+      <c r="D92" s="6" t="n">
         <v>83.8528856701782</v>
       </c>
-      <c r="E92" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F92" s="4" t="n">
+      <c r="E92" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F92" s="6" t="n">
         <v>0.41</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B93" s="3" t="n">
+      <c r="A93" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B93" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="C93" s="3" t="n">
+      <c r="C93" s="6" t="n">
         <v>0.201376663182433</v>
       </c>
-      <c r="D93" s="3" t="n">
+      <c r="D93" s="6" t="n">
         <v>88.884547319487</v>
       </c>
-      <c r="E93" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F93" s="3" t="n">
+      <c r="E93" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F93" s="6" t="n">
         <v>0.65</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B94" s="4" t="n">
+      <c r="A94" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B94" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="C94" s="4" t="n">
+      <c r="C94" s="6" t="n">
         <v>0.198753198408901</v>
       </c>
-      <c r="D94" s="4" t="n">
+      <c r="D94" s="6" t="n">
         <v>87.4393536423647</v>
       </c>
-      <c r="E94" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F94" s="4" t="n">
+      <c r="E94" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F94" s="6" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B95" s="3" t="n">
+      <c r="A95" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B95" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="C95" s="3" t="n">
+      <c r="C95" s="6" t="n">
         <v>0.216897953350467</v>
       </c>
-      <c r="D95" s="3" t="n">
+      <c r="D95" s="6" t="n">
         <v>97.6329060601429</v>
       </c>
-      <c r="E95" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F95" s="3" t="n">
+      <c r="E95" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F95" s="6" t="n">
         <v>0.23</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B96" s="4" t="n">
+      <c r="A96" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B96" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="C96" s="4" t="n">
+      <c r="C96" s="6" t="n">
         <v>0.185349782684671</v>
       </c>
-      <c r="D96" s="4" t="n">
+      <c r="D96" s="6" t="n">
         <v>80.2010445804088</v>
       </c>
-      <c r="E96" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F96" s="4" t="n">
+      <c r="E96" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F96" s="6" t="n">
         <v>0.21</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B97" s="3" t="n">
+      <c r="A97" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B97" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="C97" s="3" t="n">
+      <c r="C97" s="6" t="n">
         <v>0.214840371853695</v>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="D97" s="6" t="n">
         <v>96.4532922524588</v>
       </c>
-      <c r="E97" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F97" s="3" t="n">
+      <c r="E97" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F97" s="6" t="n">
         <v>0.065</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B98" s="4" t="n">
+      <c r="A98" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B98" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="C98" s="4" t="n">
+      <c r="C98" s="6" t="n">
         <v>0.212010609810713</v>
       </c>
-      <c r="D98" s="4" t="n">
+      <c r="D98" s="6" t="n">
         <v>94.8410484820413</v>
       </c>
-      <c r="E98" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F98" s="4" t="n">
+      <c r="E98" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F98" s="6" t="n">
         <v>0.115</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B99" s="3" t="n">
+      <c r="A99" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="C99" s="3" t="n">
+      <c r="C99" s="6" t="n">
         <v>0.209746340534592</v>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="D99" s="6" t="n">
         <v>93.5593073855043</v>
       </c>
-      <c r="E99" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F99" s="3" t="n">
+      <c r="E99" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F99" s="6" t="n">
         <v>0.77</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B100" s="4" t="n">
+      <c r="A100" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B100" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="C100" s="4" t="n">
+      <c r="C100" s="6" t="n">
         <v>0.196414246130875</v>
       </c>
-      <c r="D100" s="4" t="n">
+      <c r="D100" s="6" t="n">
         <v>86.1588466791183</v>
       </c>
-      <c r="E100" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F100" s="4" t="n">
+      <c r="E100" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F100" s="6" t="n">
         <v>0.265</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B101" s="3" t="n">
+      <c r="A101" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B101" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="C101" s="3" t="n">
+      <c r="C101" s="6" t="n">
         <v>0.21752873669712</v>
       </c>
-      <c r="D101" s="3" t="n">
+      <c r="D101" s="6" t="n">
         <v>97.9957773299769</v>
       </c>
-      <c r="E101" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F101" s="3" t="n">
+      <c r="E101" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F101" s="6" t="n">
         <v>0.575</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B102" s="4" t="n">
+      <c r="A102" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B102" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="C102" s="4" t="n">
+      <c r="C102" s="6" t="n">
         <v>0.209119227494063</v>
       </c>
-      <c r="D102" s="4" t="n">
+      <c r="D102" s="6" t="n">
         <v>93.2056136073327</v>
       </c>
-      <c r="E102" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F102" s="4" t="n">
+      <c r="E102" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F102" s="6" t="n">
         <v>0.33</v>
       </c>
     </row>
